--- a/data/trans_orig/P1422-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2012</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>29650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939501</t>
+          <t>939018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>960267</t>
+          <t>960581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1309722</t>
+          <t>1310234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1327357</t>
+          <t>1327256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2254912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2283611</t>
+          <t>2282790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945869</t>
+          <t>1945110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1958109</t>
+          <t>1958082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1740295</t>
+          <t>1740816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1752105</t>
+          <t>1752225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3690317</t>
+          <t>3691470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3707879</t>
+          <t>3708159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1418,97 +1418,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5533</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5055</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5496</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453576</t>
+          <t>453098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934317</t>
+          <t>934257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>47206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>36810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3372656</t>
+          <t>3372576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3396374</t>
+          <t>3397204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3513721</t>
+          <t>3514210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3534373</t>
+          <t>3533892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6895338</t>
+          <t>6895345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6926646</t>
+          <t>6925791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2016</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738293</t>
+          <t>738492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749968</t>
+          <t>750023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>973944</t>
+          <t>973987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>989892</t>
+          <t>989132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1719873</t>
+          <t>1718744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1737276</t>
+          <t>1736579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2060771</t>
+          <t>2059821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2073293</t>
+          <t>2073101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1975259</t>
+          <t>1973177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1986062</t>
+          <t>1985210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4039598</t>
+          <t>4040193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4056618</t>
+          <t>4056518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535539</t>
+          <t>535996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545001</t>
+          <t>545066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538430</t>
+          <t>538154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1078122</t>
+          <t>1079038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091954</t>
+          <t>1092460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34077</t>
+          <t>33115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>58589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3344253</t>
+          <t>3345478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3363745</t>
+          <t>3363281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3498023</t>
+          <t>3498985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3519700</t>
+          <t>3519573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6851742</t>
+          <t>6851129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6879655</t>
+          <t>6879357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2023</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>44675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492274</t>
+          <t>493101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504893</t>
+          <t>504809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>724630</t>
+          <t>724272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>737930</t>
+          <t>737743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1221879</t>
+          <t>1221804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240266</t>
+          <t>1240338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25009</t>
+          <t>25104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>47668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2255158</t>
+          <t>2254191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2273309</t>
+          <t>2273113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2216318</t>
+          <t>2217304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2228621</t>
+          <t>2228991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4477196</t>
+          <t>4476508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4499167</t>
+          <t>4499072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636254</t>
+          <t>636857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645229</t>
+          <t>645209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655732</t>
+          <t>655447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659886</t>
+          <t>659789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1294104</t>
+          <t>1294805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304212</t>
+          <t>1304293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54625</t>
+          <t>54097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>45457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>61261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93167</t>
+          <t>93599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3393799</t>
+          <t>3394327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3417688</t>
+          <t>3418087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3602608</t>
+          <t>3603700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3622908</t>
+          <t>3622692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7004414</t>
+          <t>7003982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7036065</t>
+          <t>7036320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1422-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29650</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57528</t>
+          <t>56078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939018</t>
+          <t>937706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>960581</t>
+          <t>960453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1310234</t>
+          <t>1309225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1327256</t>
+          <t>1327154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2254912</t>
+          <t>2256362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2282790</t>
+          <t>2283908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27079</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945110</t>
+          <t>1945038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1958082</t>
+          <t>1958003</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1740816</t>
+          <t>1740496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1752225</t>
+          <t>1751566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3691470</t>
+          <t>3690989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3708159</t>
+          <t>3707963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453098</t>
+          <t>453055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934257</t>
+          <t>933324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>46752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3372576</t>
+          <t>3373030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3397204</t>
+          <t>3396520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3514210</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3533892</t>
+          <t>3534268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6895345</t>
+          <t>6895229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6925791</t>
+          <t>6926183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738492</t>
+          <t>738435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>750023</t>
+          <t>749792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>973987</t>
+          <t>974185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>989132</t>
+          <t>989090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1718744</t>
+          <t>1717860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1736579</t>
+          <t>1737169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>23818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059821</t>
+          <t>2060318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2073101</t>
+          <t>2073317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1973177</t>
+          <t>1975115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1985210</t>
+          <t>1986127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4040193</t>
+          <t>4040867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4056518</t>
+          <t>4057174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535996</t>
+          <t>535342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545066</t>
+          <t>545036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538154</t>
+          <t>538013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1079038</t>
+          <t>1078534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092460</t>
+          <t>1092191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58589</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3345478</t>
+          <t>3346222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3363281</t>
+          <t>3363830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3498985</t>
+          <t>3499446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3519573</t>
+          <t>3519791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6851129</t>
+          <t>6851712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6879357</t>
+          <t>6879519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>37174</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44675</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>499625</t>
+          <t>562448</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>493101</t>
+          <t>554842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504809</t>
+          <t>567975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>731999</t>
+          <t>798529</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>724272</t>
+          <t>790406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>737743</t>
+          <t>804305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1231624</t>
+          <t>1360976</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1221804</t>
+          <t>1350375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240338</t>
+          <t>1369475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25104</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>50821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2264851</t>
+          <t>2202744</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2254191</t>
+          <t>2191887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2273113</t>
+          <t>2210717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2223785</t>
+          <t>2155224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2217304</t>
+          <t>2148027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2228991</t>
+          <t>2160133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4488635</t>
+          <t>4357967</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4476508</t>
+          <t>4346414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4499072</t>
+          <t>4368528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287859</t>
+          <t>2227850</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287859</t>
+          <t>2227850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287859</t>
+          <t>2227850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236317</t>
+          <t>2169386</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236317</t>
+          <t>2169386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236317</t>
+          <t>2169386</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524176</t>
+          <t>4397235</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524176</t>
+          <t>4397235</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524176</t>
+          <t>4397235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4732,27 +4732,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>642343</t>
+          <t>706949</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636857</t>
+          <t>700653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645209</t>
+          <t>710026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>658576</t>
+          <t>731775</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655447</t>
+          <t>728239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659789</t>
+          <t>733480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1300920</t>
+          <t>1438724</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1294805</t>
+          <t>1432751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304293</t>
+          <t>1442364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54097</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61261</t>
+          <t>69946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93599</t>
+          <t>100900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3406818</t>
+          <t>3472141</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3394327</t>
+          <t>3458912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3418087</t>
+          <t>3483022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3614360</t>
+          <t>3685527</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3603700</t>
+          <t>3675976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3622692</t>
+          <t>3695342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7021178</t>
+          <t>7157668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7003982</t>
+          <t>7140267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7036320</t>
+          <t>7171221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448424</t>
+          <t>3516979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448424</t>
+          <t>3516979</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448424</t>
+          <t>3516979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649157</t>
+          <t>3724188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649157</t>
+          <t>3724188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649157</t>
+          <t>3724188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7097581</t>
+          <t>7241167</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7097581</t>
+          <t>7241167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7097581</t>
+          <t>7241167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
